--- a/output/pdf_financials_xlsx/WG.xlsx
+++ b/output/pdf_financials_xlsx/WG.xlsx
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.014198</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.478276</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.722956</v>
       </c>
     </row>
     <row r="93">
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.64605</v>
+        <v>-1.094304</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.237429</v>
+        <v>-0.484588</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.796299</v>
       </c>
     </row>
     <row r="119">
@@ -3021,7 +3021,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>1.014198</v>
       </c>
@@ -3449,7 +3453,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -3935,7 +3943,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>-1.740354</v>
       </c>

--- a/output/pdf_financials_xlsx/WG.xlsx
+++ b/output/pdf_financials_xlsx/WG.xlsx
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.49397</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.420312</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.841336</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.49397</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.420312</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.841336</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.5686059999999999</v>
+        <v>0.07463599999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.438602</v>
+        <v>0.01829</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.930858</v>
+        <v>0.089522</v>
       </c>
     </row>
     <row r="49">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -2870,7 +2870,11 @@
           <t>Reclamation deposit (Note 6)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n">
         <v>0.177992</v>
       </c>
@@ -3486,7 +3490,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
